--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/pre LAM_HRM-2031-0160/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93839</v>
+        <v>17.02934</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69593</v>
+        <v>16.73961</v>
       </c>
       <c r="E2" t="n">
-        <v>16.68628</v>
+        <v>16.7547</v>
       </c>
       <c r="F2" t="n">
-        <v>42.56393</v>
+        <v>43.30256</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05175</v>
+        <v>0.05136</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8812</v>
+        <v>1.85136</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.01148</v>
+        <v>17.11992</v>
       </c>
       <c r="D3" t="n">
-        <v>16.51282</v>
+        <v>16.59277</v>
       </c>
       <c r="E3" t="n">
-        <v>16.64631</v>
+        <v>16.86783</v>
       </c>
       <c r="F3" t="n">
-        <v>42.52472</v>
+        <v>42.22382</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05135</v>
+        <v>0.05011</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83263</v>
+        <v>1.82019</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.04018</v>
+        <v>17.07482</v>
       </c>
       <c r="D4" t="n">
-        <v>16.4223</v>
+        <v>16.84452</v>
       </c>
       <c r="E4" t="n">
-        <v>16.64262</v>
+        <v>16.92211</v>
       </c>
       <c r="F4" t="n">
-        <v>43.0733</v>
+        <v>42.70763</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0513</v>
+        <v>0.05077</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8231</v>
+        <v>1.80582</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.11071</v>
+        <v>16.90363</v>
       </c>
       <c r="D6" t="n">
-        <v>15.90809</v>
+        <v>16.14213</v>
       </c>
       <c r="E6" t="n">
-        <v>16.36109</v>
+        <v>16.51572</v>
       </c>
       <c r="F6" t="n">
-        <v>21.99123</v>
+        <v>21.98016</v>
       </c>
       <c r="G6" t="n">
-        <v>34.23615</v>
+        <v>34.36837</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.57134</v>
+        <v>16.93858</v>
       </c>
       <c r="D7" t="n">
-        <v>16.19579</v>
+        <v>16.1293</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48005</v>
+        <v>16.7282</v>
       </c>
       <c r="F7" t="n">
-        <v>21.58256</v>
+        <v>21.72365</v>
       </c>
       <c r="G7" t="n">
-        <v>35.03227</v>
+        <v>34.10294</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.59541</v>
+        <v>16.87882</v>
       </c>
       <c r="D8" t="n">
-        <v>16.03679</v>
+        <v>15.81573</v>
       </c>
       <c r="E8" t="n">
-        <v>16.09294</v>
+        <v>16.73409</v>
       </c>
       <c r="F8" t="n">
-        <v>22.07479</v>
+        <v>21.81943</v>
       </c>
       <c r="G8" t="n">
-        <v>34.40406</v>
+        <v>34.27592</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60633</v>
+        <v>0.60428</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1168</v>
+        <v>1.11147</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60895</v>
+        <v>0.60695</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11776</v>
+        <v>1.1192</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60103</v>
+        <v>0.61124</v>
       </c>
       <c r="D12" t="n">
-        <v>1.14082</v>
+        <v>1.13529</v>
       </c>
     </row>
   </sheetData>
